--- a/artfynd/A 9509-2025 artfynd.xlsx
+++ b/artfynd/A 9509-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123874500</v>
+        <v>123874471</v>
       </c>
       <c r="B2" t="n">
-        <v>98502</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan., Mpd</t>
+          <t>Hammarsjön, norra sidan. Närmare sjön., Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586486</v>
+        <v>586537</v>
       </c>
       <c r="R2" t="n">
-        <v>6930971</v>
+        <v>6931042</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,7 +773,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Vid basen av tall. 10-15 meter från sjön.</t>
+          <t>Hackat på nedre delen av en låga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,7 +782,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -797,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123874593</v>
+        <v>123874525</v>
       </c>
       <c r="B3" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -841,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586524</v>
+        <v>586550</v>
       </c>
       <c r="R3" t="n">
-        <v>6931183</v>
+        <v>6931132</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -914,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123874471</v>
+        <v>123874563</v>
       </c>
       <c r="B4" t="n">
-        <v>57506</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,46 +929,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan. Närmare sjön., Mpd</t>
+          <t>Hammarsjön, norra sidan., Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586537</v>
+        <v>586532</v>
       </c>
       <c r="R4" t="n">
-        <v>6931042</v>
+        <v>6931124</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1011,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hackat på nedre delen av en låga.</t>
+          <t>Vid tall. I slänten på väg ner mot sjön från åsen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,6 +1020,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123874525</v>
+        <v>123874448</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>97375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,25 +1051,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1083,10 +1083,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586550</v>
+        <v>586595</v>
       </c>
       <c r="R5" t="n">
-        <v>6931132</v>
+        <v>6931135</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1159,7 @@
         <v>123867350</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123874563</v>
+        <v>123874500</v>
       </c>
       <c r="B7" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586532</v>
+        <v>586486</v>
       </c>
       <c r="R7" t="n">
-        <v>6931124</v>
+        <v>6930971</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Vid tall. I slänten på väg ner mot sjön från åsen.</t>
+          <t>Vid basen av tall. 10-15 meter från sjön.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,10 +1409,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123874448</v>
+        <v>123874593</v>
       </c>
       <c r="B8" t="n">
-        <v>97373</v>
+        <v>98504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1421,25 +1421,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586595</v>
+        <v>586524</v>
       </c>
       <c r="R8" t="n">
-        <v>6931135</v>
+        <v>6931183</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 9509-2025 artfynd.xlsx
+++ b/artfynd/A 9509-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1524,6 +1524,131 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123874436</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hammarsjön, norra sidan., Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>586587</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6931154</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9509-2025 artfynd.xlsx
+++ b/artfynd/A 9509-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123874471</v>
+        <v>123874563</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan. Närmare sjön., Mpd</t>
+          <t>Hammarsjön, norra sidan., Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586537</v>
+        <v>586532</v>
       </c>
       <c r="R2" t="n">
-        <v>6931042</v>
+        <v>6931124</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -773,7 +769,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hackat på nedre delen av en låga.</t>
+          <t>Vid tall. I slänten på väg ner mot sjön från åsen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,6 +778,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -800,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123874525</v>
+        <v>123874448</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>96963</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,25 +809,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586550</v>
+        <v>586595</v>
       </c>
       <c r="R3" t="n">
-        <v>6931132</v>
+        <v>6931135</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -917,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123874563</v>
+        <v>123874471</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,42 +926,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan., Mpd</t>
+          <t>Hammarsjön, norra sidan. Närmare sjön., Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586532</v>
+        <v>586537</v>
       </c>
       <c r="R4" t="n">
-        <v>6931124</v>
+        <v>6931042</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1012,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Vid tall. I slänten på väg ner mot sjön från åsen.</t>
+          <t>Hackat på nedre delen av en låga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,7 +1021,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123874448</v>
+        <v>123874500</v>
       </c>
       <c r="B5" t="n">
-        <v>97375</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,25 +1051,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1083,10 +1083,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586595</v>
+        <v>586486</v>
       </c>
       <c r="R5" t="n">
-        <v>6931135</v>
+        <v>6930971</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,6 +1129,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Vid basen av tall. 10-15 meter från sjön.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123867350</v>
+        <v>123874525</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,34 +1194,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hammarsjön, Hammarsjön, Mpd</t>
+          <t>Hammarsjön, norra sidan., Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586569</v>
+        <v>586550</v>
       </c>
       <c r="R6" t="n">
-        <v>6931145</v>
+        <v>6931132</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1245,7 +1240,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1255,12 +1250,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Norra sidan sjön. På höjden.</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,6 +1259,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1287,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123874500</v>
+        <v>123867350</v>
       </c>
       <c r="B7" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1320,24 +1311,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan., Mpd</t>
+          <t>Hammarsjön, Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586486</v>
+        <v>586569</v>
       </c>
       <c r="R7" t="n">
-        <v>6930971</v>
+        <v>6931145</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1366,7 +1367,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1376,12 +1377,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Vid basen av tall. 10-15 meter från sjön.</t>
+          <t>Norra sidan sjön. På höjden.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,7 +1391,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>123874593</v>
       </c>
       <c r="B8" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 9509-2025 artfynd.xlsx
+++ b/artfynd/A 9509-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123874563</v>
+        <v>123874471</v>
       </c>
       <c r="B2" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan., Mpd</t>
+          <t>Hammarsjön, norra sidan. Närmare sjön., Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586532</v>
+        <v>586537</v>
       </c>
       <c r="R2" t="n">
-        <v>6931124</v>
+        <v>6931042</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,7 +773,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Vid tall. I slänten på väg ner mot sjön från åsen.</t>
+          <t>Hackat på nedre delen av en låga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,7 +782,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -797,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123874448</v>
+        <v>123874593</v>
       </c>
       <c r="B3" t="n">
-        <v>96963</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,25 +812,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586595</v>
+        <v>586524</v>
       </c>
       <c r="R3" t="n">
-        <v>6931135</v>
+        <v>6931183</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -914,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123874471</v>
+        <v>123874448</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>96963</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,46 +929,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan. Närmare sjön., Mpd</t>
+          <t>Hammarsjön, norra sidan., Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586537</v>
+        <v>586595</v>
       </c>
       <c r="R4" t="n">
-        <v>6931042</v>
+        <v>6931135</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,17 +1009,13 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hackat på nedre delen av en låga.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1039,7 +1034,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123874500</v>
+        <v>123867350</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1072,24 +1067,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan., Mpd</t>
+          <t>Hammarsjön, Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586486</v>
+        <v>586569</v>
       </c>
       <c r="R5" t="n">
-        <v>6930971</v>
+        <v>6931145</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,7 +1123,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,12 +1133,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Vid basen av tall. 10-15 meter från sjön.</t>
+          <t>Norra sidan sjön. På höjden.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,7 +1147,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1161,7 +1165,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123874525</v>
+        <v>123874563</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1205,10 +1209,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586550</v>
+        <v>586532</v>
       </c>
       <c r="R6" t="n">
-        <v>6931132</v>
+        <v>6931124</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1251,6 +1255,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Vid tall. I slänten på väg ner mot sjön från åsen.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,7 +1287,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123867350</v>
+        <v>123874525</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1311,34 +1320,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hammarsjön, Hammarsjön, Mpd</t>
+          <t>Hammarsjön, norra sidan., Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586569</v>
+        <v>586550</v>
       </c>
       <c r="R7" t="n">
-        <v>6931145</v>
+        <v>6931132</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1367,7 +1366,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1377,12 +1376,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Norra sidan sjön. På höjden.</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,6 +1385,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1409,7 +1404,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123874593</v>
+        <v>123874500</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1453,10 +1448,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586524</v>
+        <v>586486</v>
       </c>
       <c r="R8" t="n">
-        <v>6931183</v>
+        <v>6930971</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1499,6 +1494,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Vid basen av tall. 10-15 meter från sjön.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 9509-2025 artfynd.xlsx
+++ b/artfynd/A 9509-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123874471</v>
+        <v>123874593</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan. Närmare sjön., Mpd</t>
+          <t>Hammarsjön, norra sidan., Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586537</v>
+        <v>586524</v>
       </c>
       <c r="R2" t="n">
-        <v>6931042</v>
+        <v>6931183</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -771,17 +767,13 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hackat på nedre delen av en låga.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -800,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123874593</v>
+        <v>123874525</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -844,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586524</v>
+        <v>586550</v>
       </c>
       <c r="R3" t="n">
-        <v>6931183</v>
+        <v>6931132</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -917,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123874448</v>
+        <v>123874563</v>
       </c>
       <c r="B4" t="n">
-        <v>96963</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -961,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586595</v>
+        <v>586532</v>
       </c>
       <c r="R4" t="n">
-        <v>6931135</v>
+        <v>6931124</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,6 +999,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Vid tall. I slänten på väg ner mot sjön från åsen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123867350</v>
+        <v>123874448</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>96963</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,55 +1043,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hammarsjön, Hammarsjön, Mpd</t>
+          <t>Hammarsjön, norra sidan., Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586569</v>
+        <v>586595</v>
       </c>
       <c r="R5" t="n">
-        <v>6931145</v>
+        <v>6931135</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1133,12 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Norra sidan sjön. På höjden.</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,6 +1129,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1165,7 +1148,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123874563</v>
+        <v>123867350</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1198,24 +1181,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan., Mpd</t>
+          <t>Hammarsjön, Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586532</v>
+        <v>586569</v>
       </c>
       <c r="R6" t="n">
-        <v>6931124</v>
+        <v>6931145</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,7 +1237,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1254,12 +1247,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Vid tall. I slänten på väg ner mot sjön från åsen.</t>
+          <t>Norra sidan sjön. På höjden.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,7 +1261,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1287,10 +1279,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123874525</v>
+        <v>123874471</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,42 +1291,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan., Mpd</t>
+          <t>Hammarsjön, norra sidan. Närmare sjön., Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586550</v>
+        <v>586537</v>
       </c>
       <c r="R7" t="n">
-        <v>6931132</v>
+        <v>6931042</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,13 +1375,17 @@
           <t>10:00</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hackat på nedre delen av en låga.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9509-2025 artfynd.xlsx
+++ b/artfynd/A 9509-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123874593</v>
+        <v>123874448</v>
       </c>
       <c r="B2" t="n">
-        <v>98079</v>
+        <v>96963</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586524</v>
+        <v>586595</v>
       </c>
       <c r="R2" t="n">
-        <v>6931183</v>
+        <v>6931135</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123874525</v>
+        <v>123874563</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586550</v>
+        <v>586532</v>
       </c>
       <c r="R3" t="n">
-        <v>6931132</v>
+        <v>6931124</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,6 +882,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Vid tall. I slänten på väg ner mot sjön från åsen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +914,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123874563</v>
+        <v>123874525</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -953,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586532</v>
+        <v>586550</v>
       </c>
       <c r="R4" t="n">
-        <v>6931124</v>
+        <v>6931132</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,11 +1004,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Vid tall. I slänten på väg ner mot sjön från åsen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123874448</v>
+        <v>123874471</v>
       </c>
       <c r="B5" t="n">
-        <v>96963</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,42 +1043,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan., Mpd</t>
+          <t>Hammarsjön, norra sidan. Närmare sjön., Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586595</v>
+        <v>586537</v>
       </c>
       <c r="R5" t="n">
-        <v>6931135</v>
+        <v>6931042</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,13 +1127,17 @@
           <t>10:00</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hackat på nedre delen av en låga.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1148,7 +1156,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123867350</v>
+        <v>123874500</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1181,34 +1189,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hammarsjön, Hammarsjön, Mpd</t>
+          <t>Hammarsjön, norra sidan., Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586569</v>
+        <v>586486</v>
       </c>
       <c r="R6" t="n">
-        <v>6931145</v>
+        <v>6930971</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1237,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,12 +1245,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Norra sidan sjön. På höjden.</t>
+          <t>Vid basen av tall. 10-15 meter från sjön.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,6 +1259,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1279,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123874471</v>
+        <v>123874593</v>
       </c>
       <c r="B7" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,46 +1290,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan. Närmare sjön., Mpd</t>
+          <t>Hammarsjön, norra sidan., Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586537</v>
+        <v>586524</v>
       </c>
       <c r="R7" t="n">
-        <v>6931042</v>
+        <v>6931183</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1375,17 +1370,13 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hackat på nedre delen av en låga.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1404,7 +1395,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123874500</v>
+        <v>123867350</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1437,24 +1428,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan., Mpd</t>
+          <t>Hammarsjön, Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586486</v>
+        <v>586569</v>
       </c>
       <c r="R8" t="n">
-        <v>6930971</v>
+        <v>6931145</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1483,7 +1484,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1493,12 +1494,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Vid basen av tall. 10-15 meter från sjön.</t>
+          <t>Norra sidan sjön. På höjden.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,7 +1508,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9509-2025 artfynd.xlsx
+++ b/artfynd/A 9509-2025 artfynd.xlsx
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123874525</v>
+        <v>123874471</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,42 +926,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan., Mpd</t>
+          <t>Hammarsjön, norra sidan. Närmare sjön., Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586550</v>
+        <v>586537</v>
       </c>
       <c r="R4" t="n">
-        <v>6931132</v>
+        <v>6931042</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,13 +1010,17 @@
           <t>10:00</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hackat på nedre delen av en låga.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1031,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123874471</v>
+        <v>123874525</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,46 +1051,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan. Närmare sjön., Mpd</t>
+          <t>Hammarsjön, norra sidan., Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586537</v>
+        <v>586550</v>
       </c>
       <c r="R5" t="n">
-        <v>6931042</v>
+        <v>6931132</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,17 +1131,13 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hackat på nedre delen av en låga.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9509-2025 artfynd.xlsx
+++ b/artfynd/A 9509-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123874448</v>
+        <v>123874593</v>
       </c>
       <c r="B2" t="n">
-        <v>96963</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586595</v>
+        <v>586524</v>
       </c>
       <c r="R2" t="n">
-        <v>6931135</v>
+        <v>6931183</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123874471</v>
+        <v>123874500</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,46 +926,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan. Närmare sjön., Mpd</t>
+          <t>Hammarsjön, norra sidan., Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586537</v>
+        <v>586486</v>
       </c>
       <c r="R4" t="n">
-        <v>6931042</v>
+        <v>6930971</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1008,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hackat på nedre delen av en låga.</t>
+          <t>Vid basen av tall. 10-15 meter från sjön.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,6 +1017,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1039,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123874525</v>
+        <v>123874448</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>96963</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,25 +1048,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1083,10 +1080,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586550</v>
+        <v>586595</v>
       </c>
       <c r="R5" t="n">
-        <v>6931132</v>
+        <v>6931135</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1156,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123874500</v>
+        <v>123867350</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1189,24 +1186,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan., Mpd</t>
+          <t>Hammarsjön, Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586486</v>
+        <v>586569</v>
       </c>
       <c r="R6" t="n">
-        <v>6930971</v>
+        <v>6931145</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1235,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,12 +1252,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Vid basen av tall. 10-15 meter från sjön.</t>
+          <t>Norra sidan sjön. På höjden.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,7 +1266,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1278,10 +1284,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123874593</v>
+        <v>123874471</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,42 +1296,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan., Mpd</t>
+          <t>Hammarsjön, norra sidan. Närmare sjön., Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586524</v>
+        <v>586537</v>
       </c>
       <c r="R7" t="n">
-        <v>6931183</v>
+        <v>6931042</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,13 +1380,17 @@
           <t>10:00</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hackat på nedre delen av en låga.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1395,7 +1409,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123867350</v>
+        <v>123874525</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1428,34 +1442,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hammarsjön, Hammarsjön, Mpd</t>
+          <t>Hammarsjön, norra sidan., Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586569</v>
+        <v>586550</v>
       </c>
       <c r="R8" t="n">
-        <v>6931145</v>
+        <v>6931132</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1484,7 +1488,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1494,12 +1498,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Norra sidan sjön. På höjden.</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,6 +1507,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9509-2025 artfynd.xlsx
+++ b/artfynd/A 9509-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123874500</v>
+        <v>123874563</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586486</v>
+        <v>586532</v>
       </c>
       <c r="R3" t="n">
-        <v>6930971</v>
+        <v>6931124</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +886,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Vid basen av tall. 10-15 meter från sjön.</t>
+          <t>Vid tall. I slänten på väg ner mot sjön från åsen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +914,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123874593</v>
+        <v>123867350</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -947,24 +947,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan., Mpd</t>
+          <t>Hammarsjön, Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586524</v>
+        <v>586569</v>
       </c>
       <c r="R4" t="n">
-        <v>6931183</v>
+        <v>6931145</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1013,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Norra sidan sjön. På höjden.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +1027,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1031,7 +1045,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123874563</v>
+        <v>123874525</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1075,10 +1089,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586532</v>
+        <v>586550</v>
       </c>
       <c r="R5" t="n">
-        <v>6931124</v>
+        <v>6931132</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,11 +1135,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Vid tall. I slänten på väg ner mot sjön från åsen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,7 +1162,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123867350</v>
+        <v>123874500</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1186,34 +1195,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hammarsjön, Hammarsjön, Mpd</t>
+          <t>Hammarsjön, norra sidan., Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586569</v>
+        <v>586486</v>
       </c>
       <c r="R6" t="n">
-        <v>6931145</v>
+        <v>6930971</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1242,7 +1241,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,12 +1251,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Norra sidan sjön. På höjden.</t>
+          <t>Vid basen av tall. 10-15 meter från sjön.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,6 +1265,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1409,7 +1409,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123874525</v>
+        <v>123874593</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586550</v>
+        <v>586524</v>
       </c>
       <c r="R8" t="n">
-        <v>6931132</v>
+        <v>6931183</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 9509-2025 artfynd.xlsx
+++ b/artfynd/A 9509-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123874448</v>
+        <v>123874563</v>
       </c>
       <c r="B2" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586595</v>
+        <v>586532</v>
       </c>
       <c r="R2" t="n">
-        <v>6931135</v>
+        <v>6931124</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,6 +765,11 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Vid tall. I slänten på väg ner mot sjön från åsen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123874563</v>
+        <v>123874471</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,42 +809,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan., Mpd</t>
+          <t>Hammarsjön, norra sidan. Närmare sjön., Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586532</v>
+        <v>586537</v>
       </c>
       <c r="R3" t="n">
-        <v>6931124</v>
+        <v>6931042</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +895,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Vid tall. I slänten på väg ner mot sjön från åsen.</t>
+          <t>Hackat på nedre delen av en låga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,7 +904,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -914,7 +922,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123867350</v>
+        <v>123874500</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -947,34 +955,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hammarsjön, Hammarsjön, Mpd</t>
+          <t>Hammarsjön, norra sidan., Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586569</v>
+        <v>586486</v>
       </c>
       <c r="R4" t="n">
-        <v>6931145</v>
+        <v>6930971</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,12 +1011,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Norra sidan sjön. På höjden.</t>
+          <t>Vid basen av tall. 10-15 meter från sjön.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,6 +1025,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1045,7 +1044,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123874525</v>
+        <v>123874593</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1089,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586550</v>
+        <v>586524</v>
       </c>
       <c r="R5" t="n">
-        <v>6931132</v>
+        <v>6931183</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1162,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123874500</v>
+        <v>123874448</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,25 +1173,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1206,10 +1205,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586486</v>
+        <v>586595</v>
       </c>
       <c r="R6" t="n">
-        <v>6930971</v>
+        <v>6931135</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1252,11 +1251,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Vid basen av tall. 10-15 meter från sjön.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123874471</v>
+        <v>123874525</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,46 +1290,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan. Närmare sjön., Mpd</t>
+          <t>Hammarsjön, norra sidan., Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586537</v>
+        <v>586550</v>
       </c>
       <c r="R7" t="n">
-        <v>6931042</v>
+        <v>6931132</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1380,17 +1370,13 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hackat på nedre delen av en låga.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1409,7 +1395,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123874593</v>
+        <v>123867350</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1442,24 +1428,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan., Mpd</t>
+          <t>Hammarsjön, Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586524</v>
+        <v>586569</v>
       </c>
       <c r="R8" t="n">
-        <v>6931183</v>
+        <v>6931145</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1488,7 +1484,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1498,7 +1494,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Norra sidan sjön. På höjden.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,7 +1508,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9509-2025 artfynd.xlsx
+++ b/artfynd/A 9509-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123874563</v>
+        <v>123874525</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586532</v>
+        <v>586550</v>
       </c>
       <c r="R2" t="n">
-        <v>6931124</v>
+        <v>6931132</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,11 +765,6 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Vid tall. I slänten på väg ner mot sjön från åsen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123874471</v>
+        <v>123874563</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,46 +804,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan. Närmare sjön., Mpd</t>
+          <t>Hammarsjön, norra sidan., Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586537</v>
+        <v>586532</v>
       </c>
       <c r="R3" t="n">
-        <v>6931042</v>
+        <v>6931124</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,7 +886,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hackat på nedre delen av en låga.</t>
+          <t>Vid tall. I slänten på väg ner mot sjön från åsen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,6 +895,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -922,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123874500</v>
+        <v>123874471</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,42 +926,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan., Mpd</t>
+          <t>Hammarsjön, norra sidan. Närmare sjön., Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586486</v>
+        <v>586537</v>
       </c>
       <c r="R4" t="n">
-        <v>6930971</v>
+        <v>6931042</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,7 +1012,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Vid basen av tall. 10-15 meter från sjön.</t>
+          <t>Hackat på nedre delen av en låga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,7 +1021,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1161,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123874448</v>
+        <v>123867350</v>
       </c>
       <c r="B6" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,45 +1168,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan., Mpd</t>
+          <t>Hammarsjön, Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586595</v>
+        <v>586569</v>
       </c>
       <c r="R6" t="n">
-        <v>6931135</v>
+        <v>6931145</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1240,7 +1245,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1250,7 +1255,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Norra sidan sjön. På höjden.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,7 +1269,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1278,10 +1287,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123874525</v>
+        <v>123874448</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,25 +1299,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1322,10 +1331,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586550</v>
+        <v>586595</v>
       </c>
       <c r="R7" t="n">
-        <v>6931132</v>
+        <v>6931135</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1395,7 +1404,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123867350</v>
+        <v>123874500</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1428,34 +1437,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hammarsjön, Hammarsjön, Mpd</t>
+          <t>Hammarsjön, norra sidan., Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586569</v>
+        <v>586486</v>
       </c>
       <c r="R8" t="n">
-        <v>6931145</v>
+        <v>6930971</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1484,7 +1483,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1494,12 +1493,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Norra sidan sjön. På höjden.</t>
+          <t>Vid basen av tall. 10-15 meter från sjön.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,6 +1507,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9509-2025 artfynd.xlsx
+++ b/artfynd/A 9509-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123874525</v>
+        <v>123867350</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -708,24 +708,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan., Mpd</t>
+          <t>Hammarsjön, Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586550</v>
+        <v>586569</v>
       </c>
       <c r="R2" t="n">
-        <v>6931132</v>
+        <v>6931145</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Norra sidan sjön. På höjden.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,7 +788,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123874563</v>
+        <v>123874471</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,42 +818,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan., Mpd</t>
+          <t>Hammarsjön, norra sidan. Närmare sjön., Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586532</v>
+        <v>586537</v>
       </c>
       <c r="R3" t="n">
-        <v>6931124</v>
+        <v>6931042</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +904,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Vid tall. I slänten på väg ner mot sjön från åsen.</t>
+          <t>Hackat på nedre delen av en låga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,7 +913,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -914,10 +931,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123874471</v>
+        <v>123874593</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,46 +943,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hammarsjön, norra sidan. Närmare sjön., Mpd</t>
+          <t>Hammarsjön, norra sidan., Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586537</v>
+        <v>586524</v>
       </c>
       <c r="R4" t="n">
-        <v>6931042</v>
+        <v>6931183</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,17 +1023,13 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hackat på nedre delen av en låga.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1039,7 +1048,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123874593</v>
+        <v>123874500</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1083,10 +1092,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586524</v>
+        <v>586486</v>
       </c>
       <c r="R5" t="n">
-        <v>6931183</v>
+        <v>6930971</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,6 +1138,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Vid basen av tall. 10-15 meter från sjön.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123867350</v>
+        <v>123874448</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,55 +1182,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hammarsjön, Hammarsjön, Mpd</t>
+          <t>Hammarsjön, norra sidan., Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586569</v>
+        <v>586595</v>
       </c>
       <c r="R6" t="n">
-        <v>6931145</v>
+        <v>6931135</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1245,7 +1249,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1255,12 +1259,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Norra sidan sjön. På höjden.</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,6 +1268,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123874448</v>
+        <v>123874563</v>
       </c>
       <c r="B7" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586595</v>
+        <v>586532</v>
       </c>
       <c r="R7" t="n">
-        <v>6931135</v>
+        <v>6931124</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1377,6 +1377,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Vid tall. I slänten på väg ner mot sjön från åsen.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,7 +1409,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123874500</v>
+        <v>123874525</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1448,10 +1453,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586486</v>
+        <v>586550</v>
       </c>
       <c r="R8" t="n">
-        <v>6930971</v>
+        <v>6931132</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1494,11 +1499,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Vid basen av tall. 10-15 meter från sjön.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 9509-2025 artfynd.xlsx
+++ b/artfynd/A 9509-2025 artfynd.xlsx
@@ -1761,7 +1761,7 @@
         <v>126835228</v>
       </c>
       <c r="B11" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>126837560</v>
       </c>
       <c r="B12" t="n">
-        <v>98395</v>
+        <v>98470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>126834909</v>
       </c>
       <c r="B19" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 9509-2025 artfynd.xlsx
+++ b/artfynd/A 9509-2025 artfynd.xlsx
@@ -1758,45 +1758,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126835228</v>
+        <v>126837444</v>
       </c>
       <c r="B11" t="n">
-        <v>98353</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586545</v>
+        <v>586492</v>
       </c>
       <c r="R11" t="n">
-        <v>6931354</v>
+        <v>6931004</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1829,6 +1834,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,10 +1865,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126837560</v>
+        <v>126835228</v>
       </c>
       <c r="B12" t="n">
-        <v>98470</v>
+        <v>98359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1866,38 +1876,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586554</v>
+        <v>586545</v>
       </c>
       <c r="R12" t="n">
-        <v>6931098</v>
+        <v>6931354</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1956,38 +1962,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126837444</v>
+        <v>126837560</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>98476</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1996,10 +2001,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586492</v>
+        <v>586554</v>
       </c>
       <c r="R13" t="n">
-        <v>6931004</v>
+        <v>6931098</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2032,11 +2037,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2170,7 +2170,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126834831</v>
+        <v>126837600</v>
       </c>
       <c r="B15" t="n">
         <v>57657</v>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586562</v>
+        <v>586602</v>
       </c>
       <c r="R15" t="n">
-        <v>6931204</v>
+        <v>6931116</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2277,7 +2277,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126837600</v>
+        <v>126834831</v>
       </c>
       <c r="B16" t="n">
         <v>57657</v>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586602</v>
+        <v>586562</v>
       </c>
       <c r="R16" t="n">
-        <v>6931116</v>
+        <v>6931204</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2601,7 +2601,7 @@
         <v>126834909</v>
       </c>
       <c r="B19" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 9509-2025 artfynd.xlsx
+++ b/artfynd/A 9509-2025 artfynd.xlsx
@@ -1758,50 +1758,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126837444</v>
+        <v>126835228</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>98359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586492</v>
+        <v>586545</v>
       </c>
       <c r="R11" t="n">
-        <v>6931004</v>
+        <v>6931354</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1834,11 +1829,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1865,10 +1855,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126835228</v>
+        <v>126837560</v>
       </c>
       <c r="B12" t="n">
-        <v>98359</v>
+        <v>98476</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1876,34 +1866,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586545</v>
+        <v>586554</v>
       </c>
       <c r="R12" t="n">
-        <v>6931354</v>
+        <v>6931098</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1962,37 +1956,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126837560</v>
+        <v>126837444</v>
       </c>
       <c r="B13" t="n">
-        <v>98476</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2001,10 +1996,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586554</v>
+        <v>586492</v>
       </c>
       <c r="R13" t="n">
-        <v>6931098</v>
+        <v>6931004</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2037,6 +2032,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 9509-2025 artfynd.xlsx
+++ b/artfynd/A 9509-2025 artfynd.xlsx
@@ -1758,45 +1758,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126835228</v>
+        <v>126837444</v>
       </c>
       <c r="B11" t="n">
-        <v>98359</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586545</v>
+        <v>586492</v>
       </c>
       <c r="R11" t="n">
-        <v>6931354</v>
+        <v>6931004</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1829,6 +1834,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1858,7 +1868,7 @@
         <v>126837560</v>
       </c>
       <c r="B12" t="n">
-        <v>98476</v>
+        <v>98477</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1956,50 +1966,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126837444</v>
+        <v>126835228</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>98360</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586492</v>
+        <v>586545</v>
       </c>
       <c r="R13" t="n">
-        <v>6931004</v>
+        <v>6931354</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2032,11 +2037,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2170,7 +2170,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126837600</v>
+        <v>126834831</v>
       </c>
       <c r="B15" t="n">
         <v>57657</v>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586602</v>
+        <v>586562</v>
       </c>
       <c r="R15" t="n">
-        <v>6931116</v>
+        <v>6931204</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2277,7 +2277,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126834831</v>
+        <v>126837600</v>
       </c>
       <c r="B16" t="n">
         <v>57657</v>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586562</v>
+        <v>586602</v>
       </c>
       <c r="R16" t="n">
-        <v>6931204</v>
+        <v>6931116</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2601,7 +2601,7 @@
         <v>126834909</v>
       </c>
       <c r="B19" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 9509-2025 artfynd.xlsx
+++ b/artfynd/A 9509-2025 artfynd.xlsx
@@ -1758,50 +1758,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126837444</v>
+        <v>126835228</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>98360</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586492</v>
+        <v>586545</v>
       </c>
       <c r="R11" t="n">
-        <v>6931004</v>
+        <v>6931354</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1834,11 +1829,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1865,37 +1855,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126837560</v>
+        <v>126837444</v>
       </c>
       <c r="B12" t="n">
-        <v>98477</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1904,10 +1895,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586554</v>
+        <v>586492</v>
       </c>
       <c r="R12" t="n">
-        <v>6931098</v>
+        <v>6931004</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,6 +1931,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1966,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126835228</v>
+        <v>126837560</v>
       </c>
       <c r="B13" t="n">
-        <v>98360</v>
+        <v>98477</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,34 +1973,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586545</v>
+        <v>586554</v>
       </c>
       <c r="R13" t="n">
-        <v>6931354</v>
+        <v>6931098</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 9509-2025 artfynd.xlsx
+++ b/artfynd/A 9509-2025 artfynd.xlsx
@@ -1758,45 +1758,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126835228</v>
+        <v>126837444</v>
       </c>
       <c r="B11" t="n">
-        <v>98360</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586545</v>
+        <v>586492</v>
       </c>
       <c r="R11" t="n">
-        <v>6931354</v>
+        <v>6931004</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1829,6 +1834,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,38 +1865,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126837444</v>
+        <v>126837560</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>98477</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1895,10 +1904,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586492</v>
+        <v>586554</v>
       </c>
       <c r="R12" t="n">
-        <v>6931004</v>
+        <v>6931098</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1931,11 +1940,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,10 +1966,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126837560</v>
+        <v>126835228</v>
       </c>
       <c r="B13" t="n">
-        <v>98477</v>
+        <v>98360</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1973,38 +1977,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586554</v>
+        <v>586545</v>
       </c>
       <c r="R13" t="n">
-        <v>6931098</v>
+        <v>6931354</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 9509-2025 artfynd.xlsx
+++ b/artfynd/A 9509-2025 artfynd.xlsx
@@ -1654,7 +1654,7 @@
         <v>126837571</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>126837444</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,10 +1865,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126837560</v>
+        <v>126835228</v>
       </c>
       <c r="B12" t="n">
-        <v>98477</v>
+        <v>98364</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1876,38 +1876,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586554</v>
+        <v>586545</v>
       </c>
       <c r="R12" t="n">
-        <v>6931098</v>
+        <v>6931354</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1966,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126835228</v>
+        <v>126837560</v>
       </c>
       <c r="B13" t="n">
-        <v>98360</v>
+        <v>98481</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,34 +1973,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586545</v>
+        <v>586554</v>
       </c>
       <c r="R13" t="n">
-        <v>6931354</v>
+        <v>6931098</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2066,7 +2066,7 @@
         <v>126837514</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2170,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126834831</v>
+        <v>126837600</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586562</v>
+        <v>586602</v>
       </c>
       <c r="R15" t="n">
-        <v>6931204</v>
+        <v>6931116</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126837600</v>
+        <v>126834831</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586602</v>
+        <v>586562</v>
       </c>
       <c r="R16" t="n">
-        <v>6931116</v>
+        <v>6931204</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2387,7 +2387,7 @@
         <v>126837580</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>126837493</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>126834909</v>
       </c>
       <c r="B19" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 9509-2025 artfynd.xlsx
+++ b/artfynd/A 9509-2025 artfynd.xlsx
@@ -2170,7 +2170,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126837600</v>
+        <v>126834831</v>
       </c>
       <c r="B15" t="n">
         <v>57661</v>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586602</v>
+        <v>586562</v>
       </c>
       <c r="R15" t="n">
-        <v>6931116</v>
+        <v>6931204</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2277,7 +2277,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126834831</v>
+        <v>126837600</v>
       </c>
       <c r="B16" t="n">
         <v>57661</v>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586562</v>
+        <v>586602</v>
       </c>
       <c r="R16" t="n">
-        <v>6931204</v>
+        <v>6931116</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
